--- a/delivery/업체전달_데이터셋_v1/01_테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_테이블정의서.xlsx
@@ -530,7 +530,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>229</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>출처</t>
+          <t>주요 응답주체</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>main_respondents</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1286,27 +1286,27 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>표4 원안</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>dim_category</t>
+          <t>dim_topic</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>주요 응답주체</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>main_respondents</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1319,10 +1319,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
@@ -1333,16 +1337,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1357,12 +1361,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
@@ -1373,16 +1377,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1397,12 +1401,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
@@ -1413,16 +1417,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1437,12 +1441,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
@@ -1453,16 +1457,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1477,32 +1481,32 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dim_topic</t>
+          <t>dim_indicator</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1517,12 +1521,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1537,16 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,12 +1561,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>C07</t>
         </is>
       </c>
     </row>
@@ -1573,16 +1577,16 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1597,12 +1601,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>교육격차·가정배경</t>
         </is>
       </c>
     </row>
@@ -1613,16 +1617,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1637,12 +1641,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>교육격차·가정배경</t>
+          <t>S0702</t>
         </is>
       </c>
     </row>
@@ -1653,16 +1657,16 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1677,12 +1681,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>S0702</t>
+          <t>사교육 참여</t>
         </is>
       </c>
     </row>
@@ -1693,16 +1697,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1717,12 +1721,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>사교육 참여</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1737,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>문항명</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>question_name</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1755,14 +1759,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>사교육 참여 유형</t>
         </is>
       </c>
     </row>
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>원영역</t>
+          <t>하위문항</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>source_area</t>
+          <t>item_name</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>여건&gt;가정 특성</t>
+          <t>1)국어, 영어, 수학 등 주요교과</t>
         </is>
       </c>
     </row>
@@ -1809,16 +1809,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>문항명</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>question_name</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1831,10 +1831,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>사교육 참여 유형</t>
+          <t>사교육 참여 유형 - 1)국어, 영어, 수학 등 주요교과</t>
         </is>
       </c>
     </row>
@@ -1845,16 +1849,16 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>하위문항</t>
+          <t>var_2021</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>item_name</t>
+          <t>var_w1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1867,10 +1871,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1주기 SPSS 원변수명</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1)국어, 영어, 수학 등 주요교과</t>
+          <t>Q10_1_1</t>
         </is>
       </c>
     </row>
@@ -1881,16 +1889,16 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>var_2025</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>var_w2</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1905,12 +1913,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>2주기 SPSS 원변수명</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>사교육 참여 유형 - 1)국어, 영어, 수학 등 주요교과</t>
+          <t>STQ7_1_1</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1929,16 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>var_2021</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>var_w1</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1945,12 +1953,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1주기 SPSS 원변수명</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Q10_1_1</t>
+          <t>binary</t>
         </is>
       </c>
     </row>
@@ -1961,16 +1969,16 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>var_2025</t>
+          <t>선지수</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>var_w2</t>
+          <t>scale_points</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1983,14 +1991,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2주기 SPSS 원변수명</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>STQ7_1_1</t>
+          <t>2→2</t>
         </is>
       </c>
     </row>
@@ -2001,32 +2005,32 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>연계판정</t>
+          <t>척도최소</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>link_grade</t>
+          <t>scale_min</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2037,36 +2041,32 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>척도최대</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>scale_max</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>선지수</t>
+          <t>척도최소라벨</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>scale_points</t>
+          <t>scale_min_label</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2096,13 +2096,13 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2→2</t>
+          <t>해당없음</t>
         </is>
       </c>
     </row>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>척도최소</t>
+          <t>척도최대라벨</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>scale_min</t>
+          <t>scale_max_label</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>참여</t>
         </is>
       </c>
     </row>
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>척도최대</t>
+          <t>긍정코드</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>scale_max</t>
+          <t>positive_code</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>척도최소라벨</t>
+          <t>역문항</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>scale_min_label</t>
+          <t>reverse_item</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2204,13 +2204,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Y=역채점 필요 / 척도 부적합 / N</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -2221,16 +2225,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>척도최대라벨</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>scale_max_label</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2240,13 +2244,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>참여</t>
         </is>
       </c>
     </row>
@@ -2257,21 +2265,21 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>긍정코드</t>
+          <t>데이터이슈</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>positive_code</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2282,7 +2290,7 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참</t>
         </is>
       </c>
     </row>
@@ -2293,16 +2301,16 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>역문항</t>
+          <t>응답기저</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>reverse_item</t>
+          <t>response_base</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2312,17 +2320,13 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Y=역채점 필요 / 척도 부적합 / N</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>선행 경험 문항(PR_CAREER_01~09)에서 '예'로 응답한 학</t>
         </is>
       </c>
     </row>
@@ -2333,16 +2337,16 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>주의사항</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>caution</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2355,34 +2359,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>2주기 0의 라벨이 "해당없음"이므로 미참여자와 무응답 구분 확인 필</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_value_label</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>주체간비교</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>cross_respondent</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2392,105 +2392,117 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>학생–학부모 [B]</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_value_label</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>needs_check</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>★연계 불가 — 제외 권장</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_value_label</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>데이터이슈</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>응답 선지 코드값</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_value_label</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>응답기저</t>
+          <t>라벨</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>response_base</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2500,38 +2512,42 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>해당 코드의 의미. 주기별로 표현이 다를 수 있음</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>선행 경험 문항(PR_CAREER_01~09)에서 '예'로 응답한 학</t>
+          <t>아니오</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>주의사항</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2539,30 +2555,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2주기 0의 라벨이 "해당없음"이므로 미참여자와 무응답 구분 확인 필</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>dim_indicator</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>출처</t>
+          <t>주기코드</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>wave_code</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2578,32 +2598,32 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>변수매칭_6_최종연계목록</t>
+          <t>W1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>dim_value_label</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>주기번호</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>wave_no</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2611,39 +2631,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>dim_value_label</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>주기명</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>wave_label</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2651,39 +2667,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>dim_value_label</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2693,32 +2705,32 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>응답 선지 코드값</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>dim_value_label</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>라벨</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2733,19 +2745,19 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>해당 코드의 의미. 주기별로 표현이 다를 수 있음</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_region</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2753,12 +2765,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2773,19 +2785,19 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_region</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2793,12 +2805,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>주기코드</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>wave_code</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2811,30 +2823,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>주기번호</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>wave_no</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2847,35 +2863,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>주기명</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>wave_label</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2883,35 +2903,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2921,37 +2945,37 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>dim_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>설립구분코드</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>found_code</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2959,34 +2983,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>dim_region</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>남녀공학코드</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>coed_code</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2999,25 +3019,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>dim_region</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -3057,21 +3073,21 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>설립구분</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>found_name</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3079,14 +3095,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>공립</t>
         </is>
       </c>
     </row>
@@ -3097,21 +3109,21 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>남녀공학</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>coed_name</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3119,14 +3131,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>남여공학</t>
         </is>
       </c>
     </row>
@@ -3137,21 +3145,21 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>학생응답</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>has_student</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3161,12 +3169,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>해당 주기에 이 학교에서 학생 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3177,21 +3185,21 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>설립구분코드</t>
+          <t>학부모응답</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>found_code</t>
+          <t>has_parent</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3199,10 +3207,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>해당 주기에 이 학교에서 학부모 응답이 수집되었는지 (Y/N)</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3213,21 +3225,21 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>남녀공학코드</t>
+          <t>교사응답</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>coed_code</t>
+          <t>has_teacher</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3235,30 +3247,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>해당 주기에 이 학교에서 교사 응답이 수집되었는지 (Y/N)</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>비교조합</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3271,34 +3287,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>학생–학부모</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>설립구분</t>
+          <t>주제</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>found_name</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3314,27 +3326,27 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>공립</t>
+          <t>전반적 학교만족도</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>남녀공학</t>
+          <t>성립여부</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>coed_name</t>
+          <t>is_valid</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3347,30 +3359,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>'성립'이면 다계열 그래프 구성 가능. '불가'는 한쪽 주체 문항이 미선택되어 단일 계열로 표시</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>남여공학</t>
+          <t>성립</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>학생응답</t>
+          <t>사유</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>has_student</t>
+          <t>invalid_reason</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3380,37 +3396,37 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>해당 주기에 이 학교에서 학생 응답이 수집되었는지 (Y/N)</t>
+          <t>성립 불가 사유. 어느 주체가 미선택인지 표기</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>학부모 문항 미포함</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>학부모응답</t>
+          <t>척도</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>has_parent</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3423,36 +3439,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>해당 주기에 이 학교에서 학부모 응답이 수집되었는지 (Y/N)</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>5점 만족도</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>교사응답</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>has_teacher</t>
-        </is>
-      </c>
+          <t>유의사항</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3463,21 +3471,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>해당 주기에 이 학교에서 교사 응답이 수집되었는지 (Y/N)</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>단일 문항이고 양 주기·양 주체 모두 불변. 대시보드 대표 지표로 가</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3485,12 +3489,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3503,17 +3507,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -3521,12 +3529,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>성립여부</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>is_valid</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3541,19 +3549,19 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>'성립'이면 다계열 그래프 구성 가능. '불가'는 한쪽 주체 문항이 미선택되어 단일 계열로 표시</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>성립</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3561,39 +3569,39 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>사유</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>invalid_reason</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>성립 불가 사유. 어느 주체가 미선택인지 표기</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>깨짐(학부모 미선택)</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -3601,12 +3609,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>비교조합</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3619,17 +3627,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>'1주기' 또는 '2주기'</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>학생–학부모</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -3637,17 +3649,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>주제</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3655,17 +3667,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>전반적 학교만족도</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -3673,10 +3689,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>학생_1주기</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>지역규모</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>region_name</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3687,17 +3707,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3705,10 +3729,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>학생_2주기</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>대분류코드</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>category_code</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3719,17 +3747,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>STQ32</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -3737,10 +3769,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>학생판정</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>대분류</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>category_name</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3751,17 +3787,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>대분류 표시명</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3769,10 +3809,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>학부모_1주기</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>소주제코드</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>topic_code</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3783,17 +3827,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -3801,10 +3849,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>학부모_2주기</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>소주제</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>topic_name</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3815,17 +3867,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>소주제 표시명</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>PRQ14</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3833,10 +3889,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>학부모판정</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>응답주체</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>respondent</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3847,17 +3907,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -3865,10 +3929,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>교사_1주기</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3879,17 +3947,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3897,10 +3969,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>교사_2주기</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>지표명</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>indicator_name</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3911,17 +3987,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -3929,10 +4009,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>교사판정</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>통계유형</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>stat_type</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3943,17 +4027,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3961,12 +4049,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>척도</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3979,17 +4067,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>5점 만족도</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -3997,28 +4089,32 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>주의사항</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>단일 문항이고 양 주기·양 주체 모두 불변. 대시보드 대표 지표로 가</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -4029,16 +4125,16 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4048,17 +4144,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
@@ -4069,21 +4165,21 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4093,12 +4189,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>8884</t>
         </is>
       </c>
     </row>
@@ -4109,16 +4205,16 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4133,12 +4229,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4149,21 +4245,21 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4173,12 +4269,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>원 척도 기준 평균</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
@@ -4189,21 +4285,21 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4213,12 +4309,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.5737</t>
         </is>
       </c>
     </row>
@@ -4229,21 +4325,21 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4253,12 +4349,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -4269,21 +4365,21 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4291,14 +4387,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
@@ -4309,21 +4401,21 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4331,14 +4423,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
@@ -4349,36 +4437,36 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>21.82</t>
         </is>
       </c>
     </row>
@@ -4389,36 +4477,36 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>7.31</t>
         </is>
       </c>
     </row>
@@ -4429,36 +4517,36 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>76.52</t>
         </is>
       </c>
     </row>
@@ -4469,36 +4557,32 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>70.6434</t>
         </is>
       </c>
     </row>
@@ -4509,36 +4593,32 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>8884.0</t>
         </is>
       </c>
     </row>
@@ -4549,36 +4629,32 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -4589,36 +4665,32 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
@@ -4629,16 +4701,16 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>headline_value</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4653,7 +4725,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -4665,20 +4737,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>headline_value_type</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4688,42 +4760,42 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4733,37 +4805,37 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4773,37 +4845,37 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>결측 응답자 수</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4813,37 +4885,37 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>원 척도 기준 평균</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>학업</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4853,37 +4925,37 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>표본표준편차</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>13.5737</t>
+          <t>S0201A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4893,37 +4965,37 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>학습동기(외재적)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4931,35 +5003,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4967,110 +5043,110 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>지표수</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>n_indicators</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>평균환산100</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>mean_scaled_100</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5080,221 +5156,229 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>평균응답수</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>mean_n_valid</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>70.6434</t>
+          <t>5923.0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>8884.0</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>진로·진학</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5309,32 +5393,32 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>S1002</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5349,32 +5433,32 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>진로·진학 준비</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5389,37 +5473,37 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>값_2021</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>value_w1</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5427,39 +5511,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>학업</t>
+          <t>59.89</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>값_2025</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>value_w2</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5467,39 +5547,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>S0201A</t>
+          <t>72.09</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>직전시점</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>prev_year</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5509,37 +5585,37 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>증감 계산의 기준이 된 이전 조사연도</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>학습동기(외재적)</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>최신시점</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>curr_year</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5549,37 +5625,37 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>증감 계산의 기준이 된 최근 조사연도</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>증감</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5587,39 +5663,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>12.2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>증감률</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>delta_pct</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5627,39 +5699,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>'1주기' 또는 '2주기'</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>20.37</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>지표수</t>
+          <t>변화방향</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>n_indicators</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5670,32 +5738,32 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>증가</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>평균환산100</t>
+          <t>절대증감순위</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>mean_scaled_100</t>
+          <t>abs_delta_rank</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5706,32 +5774,32 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>평균응답수</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>mean_n_valid</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5739,30 +5807,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>5923.0</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5777,32 +5849,32 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5817,23 +5889,23 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>PR_ASPIRE_01</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
@@ -5869,11 +5941,11 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
@@ -5909,11 +5981,11 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
@@ -5942,18 +6014,18 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>S1002</t>
+          <t>S1001</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
@@ -5982,18 +6054,18 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>진로·진학 준비</t>
+          <t>교육포부</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
@@ -6029,25 +6101,25 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>값_2021</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>value_w1</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -6055,35 +6127,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>교육포부 - 교육포부</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>값_2025</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>value_w2</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6091,35 +6167,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>직전시점</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>prev_year</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -6129,32 +6209,32 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>증감 계산의 기준이 된 이전 조사연도</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>최신시점</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>curr_year</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6169,37 +6249,37 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>증감 계산의 기준이 된 최근 조사연도</t>
+          <t>응답 선지 코드값</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>증감</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6207,30 +6287,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>152</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>증감률</t>
+          <t>비율</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>delta_pct</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6246,27 +6330,27 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>변화방향</t>
+          <t>선지라벨</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>option_label</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6276,38 +6360,38 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>증가</t>
+          <t>고등학교 졸업</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>절대증감순위</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>abs_delta_rank</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -6315,30 +6399,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6353,37 +6441,37 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -6393,32 +6481,32 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6433,37 +6521,37 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>PR_ASPIRE_01</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -6473,32 +6561,32 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6513,32 +6601,32 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>진로·진학</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6553,32 +6641,32 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>S1001</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6593,32 +6681,32 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>교육포부</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6633,32 +6721,32 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -6673,37 +6761,37 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>교육포부 - 교육포부</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -6713,32 +6801,32 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -6753,37 +6841,37 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -6793,37 +6881,37 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>응답 선지 코드값</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6833,37 +6921,37 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -6871,35 +6959,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>선지라벨</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>option_label</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6907,10 +6999,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>고등학교 졸업</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -6921,16 +7017,16 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6940,17 +7036,17 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
@@ -6961,21 +7057,21 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -6985,12 +7081,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>6985</t>
         </is>
       </c>
     </row>
@@ -7001,16 +7097,16 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -7025,12 +7121,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7041,21 +7137,21 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -7065,12 +7161,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>원 척도 기준 평균</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
@@ -7081,21 +7177,21 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -7105,12 +7201,12 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.536</t>
         </is>
       </c>
     </row>
@@ -7121,21 +7217,21 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -7145,12 +7241,12 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -7161,21 +7257,21 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -7183,14 +7279,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
@@ -7201,21 +7293,21 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -7223,14 +7315,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
@@ -7241,36 +7329,36 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>22.0</t>
         </is>
       </c>
     </row>
@@ -7281,36 +7369,36 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>7.53</t>
         </is>
       </c>
     </row>
@@ -7321,36 +7409,36 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>78.3</t>
         </is>
       </c>
     </row>
@@ -7361,36 +7449,32 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>70.6843</t>
         </is>
       </c>
     </row>
@@ -7401,36 +7485,32 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>6985.0</t>
         </is>
       </c>
     </row>
@@ -7441,36 +7521,32 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -7481,36 +7557,32 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
@@ -7521,16 +7593,16 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>headline_value</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -7545,7 +7617,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -7557,65 +7629,65 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>headline_value_type</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -7625,32 +7697,32 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -7665,37 +7737,37 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>결측 응답자 수</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -7705,37 +7777,37 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>원 척도 기준 평균</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>70.3051</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -7745,32 +7817,32 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>표본표준편차</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>13.536</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -7780,78 +7852,82 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>응답값 (코드 또는 실수)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>기저정렬(Q10=1)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -7859,222 +7935,234 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+        </is>
+      </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>70.6843</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>6985.0</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8087,30 +8175,34 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>응답값 (코드 또는 실수)</t>
+        </is>
+      </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8123,57 +8215,57 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>70.3051</t>
-        </is>
-      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -8213,7 +8305,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -8246,14 +8338,14 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -8293,7 +8385,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -8333,7 +8425,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -8366,14 +8458,14 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>PR_EDU_COST_01</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -8406,14 +8498,14 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -8446,14 +8538,14 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>기저정렬(Q10=1)</t>
+          <t>미선택→0</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2021</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -8493,7 +8585,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
@@ -8533,7 +8625,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
@@ -8566,14 +8658,14 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
@@ -8606,14 +8698,14 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>10011006</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -8653,7 +8745,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -8686,14 +8778,14 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>PR_EDU_COST_01</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
@@ -8733,7 +8825,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
@@ -8769,7 +8861,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>micro_student_2025</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
@@ -8809,7 +8901,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -8849,7 +8941,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -8882,14 +8974,14 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>교사</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
@@ -8922,14 +9014,14 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>1001001</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
@@ -8969,7 +9061,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
@@ -9002,14 +9094,14 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_01</t>
+          <t>TR_EFFICACY_01</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -9027,12 +9119,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -9042,14 +9134,14 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -9067,7 +9159,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -9080,16 +9172,12 @@
           <t>적용된 보정 내용. 공란이면 원값 그대로</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>미선택→0</t>
-        </is>
-      </c>
+      <c r="H206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2021</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -9129,7 +9217,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -9169,7 +9257,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -9202,14 +9290,14 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>교사</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -9242,14 +9330,14 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>10011006</t>
+          <t>10011491</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -9289,7 +9377,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -9322,14 +9410,14 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_01</t>
+          <t>TR_EFFICACY_01</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -9347,12 +9435,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -9362,14 +9450,14 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>micro_parent_2025</t>
+          <t>micro_teacher_2025</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -9403,672 +9491,40 @@
       <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>micro_parent_2025</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="n">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>지역규모코드</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>region_code</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>정수</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
         <is>
           <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>조사연도</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>survey_year</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>응답주체</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>respondent</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>교사</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>응답자ID</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>respondent_id</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>1001001</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>학교ID</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>school_id</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
-      <c r="H220" s="2" t="inlineStr">
-        <is>
-          <t>TR_EFFICACY_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>응답값 (코드 또는 실수)</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>결측보정</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>missing_fix</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>실수</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H222" s="2" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2021</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>지역규모코드</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>region_code</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>조사연도</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>survey_year</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>응답주체</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>respondent</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
-        </is>
-      </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>교사</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>응답자ID</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>respondent_id</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>10011491</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>학교ID</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>school_id</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>TR_EFFICACY_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F229" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>응답값 (코드 또는 실수)</t>
-        </is>
-      </c>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>결측보정</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>missing_fix</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>실수</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="3" t="inlineStr">
-        <is>
-          <t>micro_teacher_2025</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>지역규모코드</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>region_code</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
-        </is>
-      </c>
-      <c r="H231" s="3" t="inlineStr">
+      <c r="H215" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
